--- a/rules/CORE-000880/negative/01/data/unit-test-coreid-FB4006-negative.xlsx
+++ b/rules/CORE-000880/negative/01/data/unit-test-coreid-FB4006-negative.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="lb.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ae.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lb.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ae.xpt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +36,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -97,6 +103,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -552,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +593,118 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LBPDUR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-PT1H</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LBPDUR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-PT3H</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>LBPDUR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-PT5H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LBPDUR</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-PT1H</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1427,7 @@
           <t>2012-12-13T14:05</t>
         </is>
       </c>
-      <c r="T8" s="6" t="inlineStr">
+      <c r="T8" s="7" t="inlineStr">
         <is>
           <t>-PT1H</t>
         </is>
@@ -1394,7 +1515,7 @@
           <t>2012-12-26T08:44</t>
         </is>
       </c>
-      <c r="T9" s="6" t="inlineStr">
+      <c r="T9" s="7" t="inlineStr">
         <is>
           <t>-PT3H</t>
         </is>
@@ -1472,7 +1593,7 @@
           <t>2012-12-26T08:44</t>
         </is>
       </c>
-      <c r="T10" s="6" t="inlineStr">
+      <c r="T10" s="7" t="inlineStr">
         <is>
           <t>-PT5H</t>
         </is>
@@ -1550,7 +1671,7 @@
           <t>2012-12-28T09:27</t>
         </is>
       </c>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="T11" s="7" t="inlineStr">
         <is>
           <t>-PT1H</t>
         </is>
